--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_18_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_18_8.xlsx
@@ -513,1376 +513,1376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_10</t>
+          <t>model_18_8_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9973885787990261</v>
+        <v>0.9997813614247747</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7323591761687216</v>
+        <v>0.6652805554944402</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9988097645972577</v>
+        <v>0.999838817669409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9944591798347688</v>
+        <v>0.9999788797521254</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9960384082453504</v>
+        <v>0.9998588929992542</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001550252432420174</v>
+        <v>0.0001297933029484305</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1588831545078396</v>
+        <v>0.1987039213856281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005549705319756674</v>
+        <v>6.097419042931506e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.005283906745020292</v>
+        <v>8.656202169961701e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00291943863849798</v>
+        <v>3.092007620414121e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01026660571590811</v>
+        <v>0.002601425361468763</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03937324513448408</v>
+        <v>0.01139268637979781</v>
       </c>
       <c r="N2" t="n">
-        <v>1.003298637306493</v>
+        <v>1.00027617504239</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04104944569371258</v>
+        <v>0.01187769662509778</v>
       </c>
       <c r="P2" t="n">
-        <v>98.93867500337051</v>
+        <v>103.8991347003677</v>
       </c>
       <c r="Q2" t="n">
-        <v>151.3503354727031</v>
+        <v>156.3107951697003</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_9</t>
+          <t>model_18_8_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9974938975254986</v>
+        <v>0.9997964488813827</v>
       </c>
       <c r="C3" t="n">
-        <v>0.732318559300891</v>
+        <v>0.6642082657964281</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9984860143144947</v>
+        <v>0.9998015308152804</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9954534709905296</v>
+        <v>0.999906965633406</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9965793194085647</v>
+        <v>0.9998199862501355</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001487730686854047</v>
+        <v>0.0001208367369616561</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1589072664351412</v>
+        <v>0.1993404788708711</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007059254323577894</v>
+        <v>7.507955629544499e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004335718284148484</v>
+        <v>3.81304372360485e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002520821858253137</v>
+        <v>3.94455188912602e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01024340668170217</v>
+        <v>0.002603901057458001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03857111207696826</v>
+        <v>0.01099257644784225</v>
       </c>
       <c r="N3" t="n">
-        <v>1.003165603125686</v>
+        <v>1.000257117202464</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04021316417129398</v>
+        <v>0.01146055318499713</v>
       </c>
       <c r="P3" t="n">
-        <v>99.0210066979387</v>
+        <v>104.0421404095517</v>
       </c>
       <c r="Q3" t="n">
-        <v>151.4326671672713</v>
+        <v>156.4538008788843</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_11</t>
+          <t>model_18_8_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9972413002510128</v>
+        <v>0.9998082490041011</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7322891579736157</v>
+        <v>0.6631673836387041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9990184891886495</v>
+        <v>0.9997569046744076</v>
       </c>
       <c r="E4" t="n">
-        <v>0.993398353947601</v>
+        <v>0.9997789862117626</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9954180582267016</v>
+        <v>0.9997694931396379</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001637683340622913</v>
+        <v>0.0001138316743772537</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1589247203330829</v>
+        <v>0.1999583914834641</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004576486095607855</v>
+        <v>9.196132492191446e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006295544894850816</v>
+        <v>9.058321875253048e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003376596752205801</v>
+        <v>5.050982339858375e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01028658559108097</v>
+        <v>0.002619458690672106</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04046830044149263</v>
+        <v>0.01066919277064829</v>
       </c>
       <c r="N4" t="n">
-        <v>1.003484673367142</v>
+        <v>1.000242211784293</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04219111977221748</v>
+        <v>0.01112340239516853</v>
       </c>
       <c r="P4" t="n">
-        <v>98.82894526596631</v>
+        <v>104.1615794825608</v>
       </c>
       <c r="Q4" t="n">
-        <v>151.2406057352989</v>
+        <v>156.5732399518934</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_8</t>
+          <t>model_18_8_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9975519183556463</v>
+        <v>0.9998171546251571</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7321525320661555</v>
+        <v>0.6621787114096861</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9980411755557479</v>
+        <v>0.9997060755863451</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9963674851990589</v>
+        <v>0.9996024124564434</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9970299821466885</v>
+        <v>0.999709102578425</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001453287015709016</v>
+        <v>0.0001085449130156892</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1590058273736833</v>
+        <v>0.2005453100270257</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009133402025925792</v>
+        <v>0.0001111896267060448</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003464084537253355</v>
+        <v>1.629525457143909e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002188712369922967</v>
+        <v>6.374290712119127e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01021748970593621</v>
+        <v>0.002771341760557932</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03812200172746725</v>
+        <v>0.01041848899868351</v>
       </c>
       <c r="N5" t="n">
-        <v>1.003092313656026</v>
+        <v>1.000230962578749</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03974493426442813</v>
+        <v>0.01086202564460285</v>
       </c>
       <c r="P5" t="n">
-        <v>99.06785476144429</v>
+        <v>104.2566930515805</v>
       </c>
       <c r="Q5" t="n">
-        <v>151.4795152307769</v>
+        <v>156.6683535209131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_12</t>
+          <t>model_18_8_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9970578093188914</v>
+        <v>0.9998235199140257</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7321209052306816</v>
+        <v>0.6612232145171342</v>
       </c>
       <c r="D6" t="n">
-        <v>0.999119938979344</v>
+        <v>0.9996498307587599</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9922854733703248</v>
+        <v>0.999387418896623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.99473009035839</v>
+        <v>0.9996404510684729</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001746611484325693</v>
+        <v>0.0001047662025770569</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1590246024294287</v>
+        <v>0.2011125342577611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000410345660765264</v>
+        <v>0.000132466666287644</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007356824094196008</v>
+        <v>2.510683543022532e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003883584877480636</v>
+        <v>7.878617150943342e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01030254862317241</v>
+        <v>0.002924746737569721</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0417924811936991</v>
+        <v>0.0102355362623097</v>
       </c>
       <c r="N6" t="n">
-        <v>1.003716451386663</v>
+        <v>1.000222922213862</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04357167364047743</v>
+        <v>0.01067128423147724</v>
       </c>
       <c r="P6" t="n">
-        <v>98.70015532551933</v>
+        <v>104.3275586651672</v>
       </c>
       <c r="Q6" t="n">
-        <v>151.111815794852</v>
+        <v>156.7392191344998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_13</t>
+          <t>model_18_8_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.996843653088988</v>
+        <v>0.9998276493373646</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7318687587986528</v>
+        <v>0.6603148845015377</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9991229233707888</v>
+        <v>0.9995893281889703</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9911345019220146</v>
+        <v>0.9991373597550172</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9939863265044746</v>
+        <v>0.9995648348012729</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001873743873463801</v>
+        <v>0.0001023147985013496</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1591742874436398</v>
+        <v>0.2016517581928328</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004089541298933657</v>
+        <v>0.0001553543810780217</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008454427989953932</v>
+        <v>3.535559054446168e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004431691059923649</v>
+        <v>9.535558855990482e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01031406697069804</v>
+        <v>0.00306997822591429</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0432867632592667</v>
+        <v>0.01011507778029164</v>
       </c>
       <c r="N7" t="n">
-        <v>1.003986964519173</v>
+        <v>1.000217706100171</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04512957038716654</v>
+        <v>0.01054569758249624</v>
       </c>
       <c r="P7" t="n">
-        <v>98.55963355643712</v>
+        <v>104.3749124751729</v>
       </c>
       <c r="Q7" t="n">
-        <v>150.9712940257697</v>
+        <v>156.7865729445055</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_7</t>
+          <t>model_18_8_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9975574063647508</v>
+        <v>0.9998298518866797</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7318515776807235</v>
+        <v>0.6594462422486255</v>
       </c>
       <c r="D8" t="n">
-        <v>0.997470958773336</v>
+        <v>0.9995252883296405</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9971878028003802</v>
+        <v>0.9988606146671449</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9973803565678485</v>
+        <v>0.999483677644331</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001450029096434955</v>
+        <v>0.0001010072700827187</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1591844868974282</v>
+        <v>0.202167421757553</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001179214928169902</v>
+        <v>0.0001795802286850237</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002681802929580972</v>
+        <v>4.669807783149717e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001930508928875437</v>
+        <v>0.0001131391532582604</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01028712920362071</v>
+        <v>0.003209096857532147</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03807924758231122</v>
+        <v>0.01005023731474629</v>
       </c>
       <c r="N8" t="n">
-        <v>1.003085381433999</v>
+        <v>1.000214923932615</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03970035998679952</v>
+        <v>0.01047809672409435</v>
       </c>
       <c r="P8" t="n">
-        <v>99.07234331248824</v>
+        <v>104.400636125393</v>
       </c>
       <c r="Q8" t="n">
-        <v>151.4840037818209</v>
+        <v>156.8122965947256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_14</t>
+          <t>model_18_8_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9966032385046308</v>
+        <v>0.9998303830192117</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7315491309605598</v>
+        <v>0.6586040812010701</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9990366171134506</v>
+        <v>0.9994580595758809</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9899549862582617</v>
+        <v>0.9985658227897533</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9931958460918954</v>
+        <v>0.9993980687247102</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002016464356107483</v>
+        <v>0.0001006919668680275</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1593640323355354</v>
+        <v>0.2026673649348449</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0004491961101247046</v>
+        <v>0.0002050124135841721</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009579252580123794</v>
+        <v>5.878021864687001e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005014224345124249</v>
+        <v>0.0001318982106008634</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01050088023640348</v>
+        <v>0.003343561105045746</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04490505935980358</v>
+        <v>0.01003453869732074</v>
       </c>
       <c r="N9" t="n">
-        <v>1.004290646099414</v>
+        <v>1.000214253028364</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04681676070303802</v>
+        <v>0.01046172978402438</v>
       </c>
       <c r="P9" t="n">
-        <v>98.41281923985072</v>
+        <v>104.4068890686623</v>
       </c>
       <c r="Q9" t="n">
-        <v>150.8244797091833</v>
+        <v>156.8185495379949</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_6</t>
+          <t>model_18_8_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9975054216206425</v>
+        <v>0.9998294949309665</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7314117297336808</v>
+        <v>0.6578029554306226</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9967733570293525</v>
+        <v>0.9993889684017515</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9979015482945435</v>
+        <v>0.9982538286031388</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9976214778840861</v>
+        <v>0.9993092631529141</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001480889486161606</v>
+        <v>0.0001012191744137673</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1594455996392347</v>
+        <v>0.2031429477990139</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001504485383135104</v>
+        <v>0.0002311491395696011</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002001151957635951</v>
+        <v>7.156740169141982e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001752818007956308</v>
+        <v>0.00015135773445704</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01047893823235713</v>
+        <v>0.00347037220149158</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03848232693278313</v>
+        <v>0.01006077404645225</v>
       </c>
       <c r="N10" t="n">
-        <v>1.003151046373925</v>
+        <v>1.000215374824042</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04012059925971031</v>
+        <v>0.01048908202628308</v>
       </c>
       <c r="P10" t="n">
-        <v>99.03022473514707</v>
+        <v>104.3964446971328</v>
       </c>
       <c r="Q10" t="n">
-        <v>151.4418852044797</v>
+        <v>156.8081051664654</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_15</t>
+          <t>model_18_8_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9963417644280501</v>
+        <v>0.9998273473683975</v>
       </c>
       <c r="C11" t="n">
-        <v>0.731172582754316</v>
+        <v>0.657035207730285</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9988708566214723</v>
+        <v>0.9993180896968736</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9887595208473519</v>
+        <v>0.9979289256495744</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9923699108080767</v>
+        <v>0.9992176938290734</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002171686663057826</v>
+        <v>0.0001024940603245771</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1595875676167973</v>
+        <v>0.203598715998908</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00052648518101085</v>
+        <v>0.000257962076401824</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01071928736915786</v>
+        <v>8.488365474096532e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.005622885592878756</v>
+        <v>0.0001714228655713947</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01072646966859046</v>
+        <v>0.003591980805826601</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04660135902586775</v>
+        <v>0.01012393502174807</v>
       </c>
       <c r="N11" t="n">
-        <v>1.004620929143516</v>
+        <v>1.000218087534656</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04858527535771093</v>
+        <v>0.01055493189505849</v>
       </c>
       <c r="P11" t="n">
-        <v>98.26450229852223</v>
+        <v>104.3714114182355</v>
       </c>
       <c r="Q11" t="n">
-        <v>150.6761627678548</v>
+        <v>156.7830718875682</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_5</t>
+          <t>model_18_8_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9973920929954426</v>
+        <v>0.9998241708574652</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7308298939730713</v>
+        <v>0.6562907681105169</v>
       </c>
       <c r="D12" t="n">
-        <v>0.995947762750288</v>
+        <v>0.9992459417990078</v>
       </c>
       <c r="E12" t="n">
-        <v>0.998499946352994</v>
+        <v>0.9975993294627441</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9977474733263997</v>
+        <v>0.9991245898578628</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001548166253621941</v>
+        <v>0.0001043797744321275</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1597910024807287</v>
+        <v>0.2040406475153195</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001889434860518221</v>
+        <v>0.0002852551403959719</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001430500060811193</v>
+        <v>9.839226147982362e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001659967460664707</v>
+        <v>0.0001918242763414223</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01068840063643293</v>
+        <v>0.003708440990642008</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03934674387572548</v>
+        <v>0.01021664203308149</v>
       </c>
       <c r="N12" t="n">
-        <v>1.003294198321546</v>
+        <v>1.000222099969518</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04102181622150346</v>
+        <v>0.01065158563579434</v>
       </c>
       <c r="P12" t="n">
-        <v>98.94136822120176</v>
+        <v>104.3349492655543</v>
       </c>
       <c r="Q12" t="n">
-        <v>151.3530286905344</v>
+        <v>156.7466097348869</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_16</t>
+          <t>model_18_8_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9960633164983204</v>
+        <v>0.9998200651779664</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7307519749566735</v>
+        <v>0.6555971879310238</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9986350433815794</v>
+        <v>0.9991735368259175</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9875569594916188</v>
+        <v>0.9972571145956776</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9915172207385683</v>
+        <v>0.9990300777968611</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00233698538246961</v>
+        <v>0.0001068170831387158</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1598372585747886</v>
+        <v>0.2044523866709703</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000636437715516834</v>
+        <v>0.0003126454542166759</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01186608908250921</v>
+        <v>0.0001124180489255189</v>
       </c>
       <c r="K13" t="n">
-        <v>0.006251263399013024</v>
+        <v>0.0002125342348334669</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01094010348389687</v>
+        <v>0.003818457155242715</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04834237667377981</v>
+        <v>0.01033523503064714</v>
       </c>
       <c r="N13" t="n">
-        <v>1.004972652844227</v>
+        <v>1.00022728609099</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05040041173129798</v>
+        <v>0.01077522738278771</v>
       </c>
       <c r="P13" t="n">
-        <v>98.1177869565437</v>
+        <v>104.2887853794944</v>
       </c>
       <c r="Q13" t="n">
-        <v>150.5294474258763</v>
+        <v>156.700445848827</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_17</t>
+          <t>model_18_8_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.99577158851287</v>
+        <v>0.999815185505046</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7302968482369994</v>
+        <v>0.654943966428946</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9983382784611327</v>
+        <v>0.9991009641844176</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9863547750749552</v>
+        <v>0.9969084815196442</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9906454929939744</v>
+        <v>0.9989348378194626</v>
       </c>
       <c r="G14" t="n">
-        <v>0.002510167716625771</v>
+        <v>0.000109713867775184</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1601074414560378</v>
+        <v>0.2048401671723032</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000774810163011312</v>
+        <v>0.0003400991958677839</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01301253133447542</v>
+        <v>0.0001267068887497482</v>
       </c>
       <c r="K14" t="n">
-        <v>0.006893670748743365</v>
+        <v>0.0002334036980300622</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01114251458065508</v>
+        <v>0.003923259368172615</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05010157399349616</v>
+        <v>0.01047443878091729</v>
       </c>
       <c r="N14" t="n">
-        <v>1.005341151352164</v>
+        <v>1.000233449888363</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05223450172295514</v>
+        <v>0.01092035732489834</v>
       </c>
       <c r="P14" t="n">
-        <v>97.97481141739588</v>
+        <v>104.2352695664399</v>
       </c>
       <c r="Q14" t="n">
-        <v>150.3864718867285</v>
+        <v>156.6469300357725</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_4</t>
+          <t>model_18_8_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9972140211401945</v>
+        <v>0.9998096810739855</v>
       </c>
       <c r="C15" t="n">
-        <v>0.730111396246478</v>
+        <v>0.6543161410477221</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9949948481775392</v>
+        <v>0.9990284620110449</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9989762921805955</v>
+        <v>0.9965588043986772</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9977542200856758</v>
+        <v>0.9988395556822479</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001653877399200862</v>
+        <v>0.0001129815358317354</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1602175337687202</v>
+        <v>0.2052128714392422</v>
       </c>
       <c r="I15" t="n">
-        <v>0.002333749914621997</v>
+        <v>0.0003675262799008818</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0009762411503308603</v>
+        <v>0.0001410385190945844</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001654995532476429</v>
+        <v>0.0002542823994977332</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01100403401324369</v>
+        <v>0.004023219101445233</v>
       </c>
       <c r="M15" t="n">
-        <v>0.04066789150178383</v>
+        <v>0.01062927729583415</v>
       </c>
       <c r="N15" t="n">
-        <v>1.003519131191333</v>
+        <v>1.000240402853913</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04239920783715573</v>
+        <v>0.01108178763595513</v>
       </c>
       <c r="P15" t="n">
-        <v>98.80926561789693</v>
+        <v>104.1765723046446</v>
       </c>
       <c r="Q15" t="n">
-        <v>151.2209260872295</v>
+        <v>156.5882327739772</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_18</t>
+          <t>model_18_8_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9954700532530426</v>
+        <v>0.9998036594533241</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7298158619020496</v>
+        <v>0.65371904905764</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9979892876326667</v>
+        <v>0.9989564392933733</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9851602556787693</v>
+        <v>0.9962087421883467</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9897622026828899</v>
+        <v>0.9987446550007385</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00268917207250431</v>
+        <v>0.0001165562299768233</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1603929757219918</v>
+        <v>0.2055673310375858</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0009375339614146928</v>
+        <v>0.0003947719890703585</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01415166397302777</v>
+        <v>0.000155385932452029</v>
       </c>
       <c r="K16" t="n">
-        <v>0.007544598967221234</v>
+        <v>0.0002750775144713952</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01133365289483818</v>
+        <v>0.004118332390692444</v>
       </c>
       <c r="M16" t="n">
-        <v>0.05185722777496219</v>
+        <v>0.01079612106160464</v>
       </c>
       <c r="N16" t="n">
-        <v>1.005722037996157</v>
+        <v>1.000248009111591</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05406489732060252</v>
+        <v>0.01125573428624868</v>
       </c>
       <c r="P16" t="n">
-        <v>97.83704382496094</v>
+        <v>104.114273481313</v>
       </c>
       <c r="Q16" t="n">
-        <v>150.2487042942936</v>
+        <v>156.5259339506456</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_19</t>
+          <t>model_18_8_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9951618534136191</v>
+        <v>0.999797226840809</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7293164434175708</v>
+        <v>0.6531506526924918</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9975963615127067</v>
+        <v>0.9988850993551156</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9839796861758607</v>
+        <v>0.9958606919054321</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9888740372324303</v>
+        <v>0.9986505255400504</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002872132810725937</v>
+        <v>0.000120374906640183</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1606894521081336</v>
+        <v>0.2059047556733823</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001120743448646315</v>
+        <v>0.0004217594073846925</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01527749353857249</v>
+        <v>0.0001696508863110431</v>
       </c>
       <c r="K17" t="n">
-        <v>0.008199119850249532</v>
+        <v>0.0002957036356570958</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01151420012024006</v>
+        <v>0.004208969609535007</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05359228312663995</v>
+        <v>0.01097154987411455</v>
       </c>
       <c r="N17" t="n">
-        <v>1.006111343056481</v>
+        <v>1.000256134516873</v>
       </c>
       <c r="O17" t="n">
-        <v>0.05587381757066092</v>
+        <v>0.01143863146649484</v>
       </c>
       <c r="P17" t="n">
-        <v>97.70540077115274</v>
+        <v>104.0497989268422</v>
       </c>
       <c r="Q17" t="n">
-        <v>150.1170612404854</v>
+        <v>156.4614593961748</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_3</t>
+          <t>model_18_8_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9969685291491457</v>
+        <v>0.9997904843383341</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7292711008515834</v>
+        <v>0.6526066107819027</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9939158266332682</v>
+        <v>0.9988146003749807</v>
       </c>
       <c r="E18" t="n">
-        <v>0.999326829581328</v>
+        <v>0.9955184741428958</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9976396715699406</v>
+        <v>0.9985576602533957</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001799612049789243</v>
+        <v>0.0001243775473702287</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1607163694140006</v>
+        <v>0.2062277224528948</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002836864810261658</v>
+        <v>0.0004484286969033248</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0006419572571744837</v>
+        <v>0.0001836767924285069</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001739410430207246</v>
+        <v>0.0003160527446659158</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01142763696289967</v>
+        <v>0.004295572671710025</v>
       </c>
       <c r="M18" t="n">
-        <v>0.04242183458773611</v>
+        <v>0.01115246821874999</v>
       </c>
       <c r="N18" t="n">
-        <v>1.003829226337921</v>
+        <v>1.000264651362104</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04422781991143971</v>
+        <v>0.01162725187961402</v>
       </c>
       <c r="P18" t="n">
-        <v>98.64036833040872</v>
+        <v>103.9843777626532</v>
       </c>
       <c r="Q18" t="n">
-        <v>151.0520287997413</v>
+        <v>156.3960382319858</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_20</t>
+          <t>model_18_8_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9948492498924196</v>
+        <v>0.9997834808304858</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7288051510099123</v>
+        <v>0.6520918631984267</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9971666329522489</v>
+        <v>0.9987454079604227</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9828164953016462</v>
+        <v>0.9951774467473251</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9879854771721859</v>
+        <v>0.9984660410017356</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00305770776467892</v>
+        <v>0.0001285351321647253</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1609929773680017</v>
+        <v>0.206533298854384</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001321112793443887</v>
+        <v>0.0004746037214612624</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01638675027723664</v>
+        <v>0.0001976539109693682</v>
       </c>
       <c r="K19" t="n">
-        <v>0.008853931535340264</v>
+        <v>0.0003361288162153153</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01168473974188346</v>
+        <v>0.004377521224994169</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05529654387643879</v>
+        <v>0.01133733355620823</v>
       </c>
       <c r="N19" t="n">
-        <v>1.006506210662207</v>
+        <v>1.000273497898334</v>
       </c>
       <c r="O19" t="n">
-        <v>0.05765063222888479</v>
+        <v>0.01181998731721186</v>
       </c>
       <c r="P19" t="n">
-        <v>97.58017948048199</v>
+        <v>103.9186165778728</v>
       </c>
       <c r="Q19" t="n">
-        <v>149.9918399498146</v>
+        <v>156.3302770472054</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_2</t>
+          <t>model_18_8_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9966535023686323</v>
+        <v>0.9997764473725823</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7283213508225914</v>
+        <v>0.6515696742359822</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9927108548116317</v>
+        <v>0.998676939840156</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9995515869853976</v>
+        <v>0.9948610103041161</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9974038932887174</v>
+        <v>0.9983773390265948</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001986625555150368</v>
+        <v>0.0001327104966057987</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1612801820582752</v>
+        <v>0.2068432927798796</v>
       </c>
       <c r="I20" t="n">
-        <v>0.003398706485722306</v>
+        <v>0.0005005047503654246</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0004276212693710138</v>
+        <v>0.0002106231613428751</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00191316387754666</v>
+        <v>0.0003555656394510113</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01188348636917562</v>
+        <v>0.004456564933814681</v>
       </c>
       <c r="M20" t="n">
-        <v>0.04457157788490743</v>
+        <v>0.01152000419295925</v>
       </c>
       <c r="N20" t="n">
-        <v>1.00422715490278</v>
+        <v>1.000282382266212</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04646908223135372</v>
+        <v>0.01201043462114971</v>
       </c>
       <c r="P20" t="n">
-        <v>98.44263556100672</v>
+        <v>103.8546810389692</v>
       </c>
       <c r="Q20" t="n">
-        <v>150.8542960303394</v>
+        <v>156.2663415083018</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_21</t>
+          <t>model_18_8_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9945347202660817</v>
+        <v>0.9997691537019108</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7282871725036895</v>
+        <v>0.6511021194964546</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9967070667335616</v>
+        <v>0.9986104219081172</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9816754432275701</v>
+        <v>0.9945333380496346</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9871018002896971</v>
+        <v>0.9982892887314442</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003244426137845496</v>
+        <v>0.0001370403345865747</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1613004717848019</v>
+        <v>0.2071208534705763</v>
       </c>
       <c r="I21" t="n">
-        <v>0.001535394529876298</v>
+        <v>0.0005256680361935041</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01747489473434493</v>
+        <v>0.0002240529150897082</v>
       </c>
       <c r="K21" t="n">
-        <v>0.009505144632110612</v>
+        <v>0.0003748596632872797</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01184566072670886</v>
+        <v>0.004530879863422988</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0569598642716562</v>
+        <v>0.01170642279206482</v>
       </c>
       <c r="N21" t="n">
-        <v>1.006903511242844</v>
+        <v>1.000291595323902</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0593847636168745</v>
+        <v>0.01220478944595891</v>
       </c>
       <c r="P21" t="n">
-        <v>97.46163357900984</v>
+        <v>103.7904705248529</v>
       </c>
       <c r="Q21" t="n">
-        <v>149.8732940483425</v>
+        <v>156.2021309941856</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_22</t>
+          <t>model_18_8_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.99421980641892</v>
+        <v>0.9997618310717489</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7277673641607407</v>
+        <v>0.6506521709223274</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9962232918650525</v>
+        <v>0.9985454434566202</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9805583983519103</v>
+        <v>0.994216111607289</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9862259981035357</v>
+        <v>0.9982035290999866</v>
       </c>
       <c r="G22" t="n">
-        <v>0.003431372601090547</v>
+        <v>0.0001413873641718732</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1616090524717275</v>
+        <v>0.2073879623809446</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001760964022696246</v>
+        <v>0.0005502489468978726</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01854014514438829</v>
+        <v>0.0002370545438343424</v>
       </c>
       <c r="K22" t="n">
-        <v>0.01015055458354227</v>
+        <v>0.0003936517453661075</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01199789992998608</v>
+        <v>0.004601550832983933</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05857791905735937</v>
+        <v>0.01189064187383815</v>
       </c>
       <c r="N22" t="n">
-        <v>1.007301297155048</v>
+        <v>1.000300844962001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06107170234464022</v>
+        <v>0.01239685111542939</v>
       </c>
       <c r="P22" t="n">
-        <v>97.34958984521597</v>
+        <v>103.7280143415742</v>
       </c>
       <c r="Q22" t="n">
-        <v>149.7612503145486</v>
+        <v>156.1396748109069</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_1</t>
+          <t>model_18_8_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9962667466039518</v>
+        <v>0.9997545165905197</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7272793878014254</v>
+        <v>0.6502208844519827</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9913780159721368</v>
+        <v>0.9984819804488908</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9996523886930996</v>
+        <v>0.9939103237429407</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9970474616935824</v>
+        <v>0.9981201510328378</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002216220484043823</v>
+        <v>0.0001457295561986379</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1618987363180982</v>
+        <v>0.2076439926603466</v>
       </c>
       <c r="I23" t="n">
-        <v>0.004020168658741204</v>
+        <v>0.000574256575428402</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0003314934746848957</v>
+        <v>0.0002495873587455897</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00217583106671305</v>
+        <v>0.0004119219670869959</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01237355145367545</v>
+        <v>0.004669013417903793</v>
       </c>
       <c r="M23" t="n">
-        <v>0.04707675099286083</v>
+        <v>0.01207184974221589</v>
       </c>
       <c r="N23" t="n">
-        <v>1.004715688500271</v>
+        <v>1.000310084306712</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04908090574493595</v>
+        <v>0.01258577337791598</v>
       </c>
       <c r="P23" t="n">
-        <v>98.22390403727374</v>
+        <v>103.667516017581</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.6355645066064</v>
+        <v>156.0791764869136</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_23</t>
+          <t>model_18_8_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9939062216958365</v>
+        <v>0.9997471945563294</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7272489414692844</v>
+        <v>0.649812092348178</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9957207825014929</v>
+        <v>0.9984202282789739</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9794679661212309</v>
+        <v>0.9936106749173264</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9853614881914297</v>
+        <v>0.9980388238699349</v>
       </c>
       <c r="G24" t="n">
-        <v>0.003617530038867629</v>
+        <v>0.0001500762319893945</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1619168105760702</v>
+        <v>0.2078866693120645</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00199526884019278</v>
+        <v>0.0005976170055334108</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01958001686858343</v>
+        <v>0.0002618685631609476</v>
       </c>
       <c r="K24" t="n">
-        <v>0.01078764285438811</v>
+        <v>0.0004297427843471792</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01214160940108122</v>
+        <v>0.004733045018262592</v>
       </c>
       <c r="M24" t="n">
-        <v>0.06014590625194394</v>
+        <v>0.01225056047654125</v>
       </c>
       <c r="N24" t="n">
-        <v>1.00769740417368</v>
+        <v>1.000319333192005</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06270644200027919</v>
+        <v>0.01277209219818378</v>
       </c>
       <c r="P24" t="n">
-        <v>97.24392759145746</v>
+        <v>103.608734359404</v>
       </c>
       <c r="Q24" t="n">
-        <v>149.6555880607901</v>
+        <v>156.0203948287366</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_24</t>
+          <t>model_18_8_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9935958072467114</v>
+        <v>0.999739890373169</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7267345296375051</v>
+        <v>0.6494241996700643</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9952050641937666</v>
+        <v>0.9983602116951293</v>
       </c>
       <c r="E25" t="n">
-        <v>0.978407466676055</v>
+        <v>0.9933166799201562</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9845121683568614</v>
+        <v>0.9979595195811501</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003801805465074336</v>
+        <v>0.0001544123106376731</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1622221876608485</v>
+        <v>0.208116939161884</v>
       </c>
       <c r="I25" t="n">
-        <v>0.002235732586212263</v>
+        <v>0.0006203208751128795</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0205913437126882</v>
+        <v>0.000273918043581695</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01141353701386863</v>
+        <v>0.0004471203392493589</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01227722008164537</v>
+        <v>0.004794163634775819</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0616587825461575</v>
+        <v>0.01242627501054411</v>
       </c>
       <c r="N25" t="n">
-        <v>1.008089506635733</v>
+        <v>1.000328559528629</v>
       </c>
       <c r="O25" t="n">
-        <v>0.06428372457042308</v>
+        <v>0.01295528726367838</v>
       </c>
       <c r="P25" t="n">
-        <v>97.14455840539344</v>
+        <v>103.5517683828855</v>
       </c>
       <c r="Q25" t="n">
-        <v>149.5562188747261</v>
+        <v>155.9634288522181</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_18_8_0</t>
+          <t>model_18_8_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9958060693602155</v>
+        <v>0.9997327267063503</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7261637323469117</v>
+        <v>0.6490505086871849</v>
       </c>
       <c r="D26" t="n">
-        <v>0.989913893394732</v>
+        <v>0.998302001924217</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9996322718574738</v>
+        <v>0.9930369447972779</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9965712631251403</v>
+        <v>0.9978831165363165</v>
       </c>
       <c r="G26" t="n">
-        <v>0.002489698396146407</v>
+        <v>0.00015866497271558</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1625610375897038</v>
+        <v>0.2083387782719311</v>
       </c>
       <c r="I26" t="n">
-        <v>0.004702844441857536</v>
+        <v>0.0006423412395253215</v>
       </c>
       <c r="J26" t="n">
-        <v>0.000350677544963561</v>
+        <v>0.0002853830784243316</v>
       </c>
       <c r="K26" t="n">
-        <v>0.002526758821617524</v>
+        <v>0.0004638621589748266</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01289966972815534</v>
+        <v>0.004852016256206611</v>
       </c>
       <c r="M26" t="n">
-        <v>0.04989687761920987</v>
+        <v>0.01259622851156567</v>
       </c>
       <c r="N26" t="n">
-        <v>1.005297596597623</v>
+        <v>1.000337608370926</v>
       </c>
       <c r="O26" t="n">
-        <v>0.05202109100023557</v>
+        <v>0.01313247603709068</v>
       </c>
       <c r="P26" t="n">
-        <v>97.99118740377499</v>
+        <v>103.4974313372405</v>
       </c>
       <c r="Q26" t="n">
-        <v>150.4028478731076</v>
+        <v>155.9090918065731</v>
       </c>
     </row>
   </sheetData>
